--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F379"/>
+  <dimension ref="A1:F401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8780,6 +8780,490 @@
         <v>56.8</v>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="D380" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="E380" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="F380" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="D381" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="E381" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="F381" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D382" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E382" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="F382" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="D383" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="E383" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="F383" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="D384" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="E384" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="F384" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="D385" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="E385" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F385" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="D386" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="E386" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="F386" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="D387" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E387" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="F387" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="D388" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="E388" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="F388" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="D389" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E389" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="F389" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="D390" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="E390" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="F390" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="D391" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E391" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="F391" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="D392" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="E392" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="F392" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D393" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="E393" t="n">
+        <v>56.42</v>
+      </c>
+      <c r="F393" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>50.84</v>
+      </c>
+      <c r="D394" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="E394" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="F394" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D395" t="n">
+        <v>57.38</v>
+      </c>
+      <c r="E395" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="F395" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="D396" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="E396" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="F396" t="n">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="D397" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="E397" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="F397" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="D398" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="E398" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="F398" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="D399" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="E399" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="F399" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="D400" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="E400" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="F400" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="D401" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="E401" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="F401" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F401"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9264,6 +9264,534 @@
         <v>56.8</v>
       </c>
     </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D402" t="n">
+        <v>50.61</v>
+      </c>
+      <c r="E402" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="F402" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="D403" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E403" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F403" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>50.63</v>
+      </c>
+      <c r="D404" t="n">
+        <v>50.83</v>
+      </c>
+      <c r="E404" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="F404" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D405" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="E405" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="F405" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="D406" t="n">
+        <v>50.54</v>
+      </c>
+      <c r="E406" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="F406" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="D407" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="E407" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="F407" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="D408" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="E408" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="F408" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="D409" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="E409" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="F409" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>50.59</v>
+      </c>
+      <c r="D410" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="E410" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="F410" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="D411" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E411" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="F411" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>50.74</v>
+      </c>
+      <c r="D412" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="E412" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="F412" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>57</v>
+      </c>
+      <c r="D413" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="E413" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="F413" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="D414" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="E414" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="F414" t="n">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="D415" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="E415" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="F415" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="D416" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="E416" t="n">
+        <v>50.21</v>
+      </c>
+      <c r="F416" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="D417" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="E417" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="F417" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="D418" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="E418" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="F418" t="n">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="D419" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="E419" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="F419" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D420" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="E420" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="F420" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="D421" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="E421" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F421" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="D422" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="E422" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="F422" t="n">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="D423" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="E423" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="F423" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="D424" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="E424" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="F424" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D425" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="E425" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="F425" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F425"/>
+  <dimension ref="A1:F507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9792,6 +9792,1810 @@
         <v>56.7</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="D426" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="E426" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="F426" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="D427" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="E427" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="F427" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="D428" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="E428" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="F428" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="D429" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="E429" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="F429" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="D430" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="E430" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="F430" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="D431" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="E431" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="F431" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>49.77</v>
+      </c>
+      <c r="D432" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="E432" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="F432" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="D433" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="E433" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="F433" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D434" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="E434" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F434" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D435" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E435" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="F435" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D436" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="E436" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="F436" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D437" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="E437" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="F437" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="D438" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="E438" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="F438" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="D439" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="E439" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="F439" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="D440" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="E440" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F440" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="D441" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="E441" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="F441" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="D442" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="E442" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="F442" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D443" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="E443" t="n">
+        <v>56.31</v>
+      </c>
+      <c r="F443" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>48.79</v>
+      </c>
+      <c r="D444" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="E444" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="F444" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="D445" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="E445" t="n">
+        <v>56.29</v>
+      </c>
+      <c r="F445" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="D446" t="n">
+        <v>49.19</v>
+      </c>
+      <c r="E446" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="F446" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="D447" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="E447" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="F447" t="n">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D448" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="E448" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="F448" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="D449" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="E449" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F449" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="D450" t="n">
+        <v>50</v>
+      </c>
+      <c r="E450" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="F450" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="D451" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="E451" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="F451" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="D452" t="n">
+        <v>50.38</v>
+      </c>
+      <c r="E452" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="F452" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="D453" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="E453" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="F453" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D454" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E454" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="F454" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="D455" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="E455" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="F455" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="D456" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="E456" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="F456" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D457" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="E457" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="F457" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="D458" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="E458" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="F458" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="D459" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="E459" t="n">
+        <v>56.62</v>
+      </c>
+      <c r="F459" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="D460" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E460" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="F460" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="D461" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="E461" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="F461" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="D462" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="E462" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="F462" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D463" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E463" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="F463" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="D464" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="E464" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="F464" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D465" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="E465" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="F465" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D466" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="E466" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F466" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="D467" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="E467" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="F467" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="D468" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="E468" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F468" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="D469" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E469" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F469" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="D470" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="E470" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="F470" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="D471" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="E471" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="F471" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="D472" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E472" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="F472" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D473" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="E473" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="F473" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D474" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E474" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F474" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D475" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="E475" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="F475" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D476" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E476" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F476" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="D477" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="E477" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="F477" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D478" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E478" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F478" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="D479" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="E479" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F479" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="D480" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="E480" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="F480" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D481" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="E481" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="F481" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="D482" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="E482" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F482" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D483" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="E483" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="F483" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="D484" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="E484" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="F484" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="D485" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E485" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="F485" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="D486" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="E486" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F486" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="D487" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="E487" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="F487" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="D488" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="E488" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="F488" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="D489" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E489" t="n">
+        <v>56.81</v>
+      </c>
+      <c r="F489" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="D490" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="E490" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="F490" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>45928</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="D491" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="E491" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="F491" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="D492" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E492" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="F492" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="D493" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="E493" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F493" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="D494" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="E494" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="F494" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="D495" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="E495" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="F495" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="D496" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E496" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="F496" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D497" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="E497" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F497" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="D498" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="E498" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F498" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="D499" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E499" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F499" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="D500" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="E500" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="F500" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>45941</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="D501" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="E501" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="F501" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>49.56</v>
+      </c>
+      <c r="D502" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="E502" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="F502" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="D503" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E503" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F503" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="D504" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="E504" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="F504" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="D505" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="E505" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="F505" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="D506" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="E506" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="F506" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="D507" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E507" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="F507" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F507"/>
+  <dimension ref="A1:F553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11596,6 +11596,1018 @@
         <v>57.4</v>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="D508" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E508" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="F508" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D509" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="E509" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F509" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="D510" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="E510" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F510" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D511" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E511" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="F511" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D512" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E512" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F512" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="D513" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="E513" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="F513" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D514" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E514" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F514" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="D515" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="E515" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F515" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="D516" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="E516" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="F516" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="D517" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="E517" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="F517" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="D518" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="E518" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="F518" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D519" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="E519" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="F519" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="D520" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="E520" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="F520" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="D521" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="E521" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="F521" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="D522" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="E522" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F522" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="D523" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E523" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="F523" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="D524" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="E524" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="F524" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="D525" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="E525" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F525" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="D526" t="n">
+        <v>49.21</v>
+      </c>
+      <c r="E526" t="n">
+        <v>48.97</v>
+      </c>
+      <c r="F526" t="n">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="D527" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E527" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F527" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="D528" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="E528" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="F528" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="D529" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="E529" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="F529" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="D530" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="E530" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="F530" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D531" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="E531" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="F531" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="D532" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="E532" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="F532" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="D533" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="E533" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="F533" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="D534" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="E534" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="F534" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>57.02</v>
+      </c>
+      <c r="D535" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="E535" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="F535" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D536" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="E536" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="F536" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="D537" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E537" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="F537" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="D538" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="E538" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="F538" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="D539" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="E539" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="F539" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="D540" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="E540" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="F540" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="D541" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="E541" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="F541" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="D542" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="E542" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="F542" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="D543" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="E543" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="F543" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="D544" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="E544" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F544" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D545" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="E545" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F545" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="D546" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="E546" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="F546" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D547" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E547" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="F547" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="D548" t="n">
+        <v>48.36</v>
+      </c>
+      <c r="E548" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="F548" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="D549" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="E549" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="F549" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="D550" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="E550" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="F550" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>57.21</v>
+      </c>
+      <c r="D551" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="E551" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F551" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="D552" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="E552" t="n">
+        <v>48.69</v>
+      </c>
+      <c r="F552" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>45976</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="D553" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="E553" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="F553" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F553"/>
+  <dimension ref="A1:F623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11373,7 +11373,7 @@
         <v>57.01</v>
       </c>
       <c r="F497" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="498">
@@ -11417,7 +11417,7 @@
         <v>56.78</v>
       </c>
       <c r="F499" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="500">
@@ -11461,7 +11461,7 @@
         <v>57.05</v>
       </c>
       <c r="F501" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="502">
@@ -11505,7 +11505,7 @@
         <v>56.89</v>
       </c>
       <c r="F503" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="504">
@@ -11549,7 +11549,7 @@
         <v>57.26</v>
       </c>
       <c r="F505" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="506">
@@ -11593,7 +11593,7 @@
         <v>56.83</v>
       </c>
       <c r="F507" t="n">
-        <v>57.4</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="508">
@@ -11637,7 +11637,7 @@
         <v>57.3</v>
       </c>
       <c r="F509" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="510">
@@ -11681,7 +11681,7 @@
         <v>57.25</v>
       </c>
       <c r="F511" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="512">
@@ -11725,7 +11725,7 @@
         <v>56.96</v>
       </c>
       <c r="F513" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="514">
@@ -11769,7 +11769,7 @@
         <v>57.09</v>
       </c>
       <c r="F515" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="516">
@@ -11813,7 +11813,7 @@
         <v>57.16</v>
       </c>
       <c r="F517" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="518">
@@ -11857,7 +11857,7 @@
         <v>57.29</v>
       </c>
       <c r="F519" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="520">
@@ -11901,7 +11901,7 @@
         <v>57.07</v>
       </c>
       <c r="F521" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="522">
@@ -11945,7 +11945,7 @@
         <v>56.9</v>
       </c>
       <c r="F523" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="524">
@@ -11989,7 +11989,7 @@
         <v>57.11</v>
       </c>
       <c r="F525" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="526">
@@ -12033,7 +12033,7 @@
         <v>57.08</v>
       </c>
       <c r="F527" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="528">
@@ -12077,7 +12077,7 @@
         <v>57.14</v>
       </c>
       <c r="F529" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="530">
@@ -12121,7 +12121,7 @@
         <v>57.33</v>
       </c>
       <c r="F531" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="532">
@@ -12165,7 +12165,7 @@
         <v>57.22</v>
       </c>
       <c r="F533" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="534">
@@ -12209,7 +12209,7 @@
         <v>56.77</v>
       </c>
       <c r="F535" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="536">
@@ -12253,7 +12253,7 @@
         <v>57.46</v>
       </c>
       <c r="F537" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="538">
@@ -12297,7 +12297,7 @@
         <v>57.43</v>
       </c>
       <c r="F539" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="540">
@@ -12341,7 +12341,7 @@
         <v>57.22</v>
       </c>
       <c r="F541" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="542">
@@ -12385,7 +12385,7 @@
         <v>57.12</v>
       </c>
       <c r="F543" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="544">
@@ -12429,7 +12429,7 @@
         <v>57.11</v>
       </c>
       <c r="F545" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="546">
@@ -12473,7 +12473,7 @@
         <v>57.25</v>
       </c>
       <c r="F547" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="548">
@@ -12517,7 +12517,7 @@
         <v>56.96</v>
       </c>
       <c r="F549" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="550">
@@ -12561,7 +12561,7 @@
         <v>57.09</v>
       </c>
       <c r="F551" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="552">
@@ -12605,7 +12605,1547 @@
         <v>57.16</v>
       </c>
       <c r="F553" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="D554" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E554" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="F554" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="D555" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="E555" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F555" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>49.63</v>
+      </c>
+      <c r="D556" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E556" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="F556" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="D557" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E557" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F557" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="D558" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E558" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F558" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="D559" t="n">
+        <v>57.76</v>
+      </c>
+      <c r="E559" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="F559" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="D560" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E560" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="F560" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="D561" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="E561" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="F561" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="D562" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="E562" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="F562" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="D563" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="E563" t="n">
+        <v>57.16</v>
+      </c>
+      <c r="F563" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="D564" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="E564" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="F564" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
         <v>57.5</v>
+      </c>
+      <c r="D565" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="E565" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="F565" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="D566" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E566" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F566" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="D567" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="E567" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="F567" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="D568" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="E568" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="F568" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="D569" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="E569" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="F569" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="D570" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="E570" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="F570" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="D571" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="E571" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F571" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="D572" t="n">
+        <v>48.92</v>
+      </c>
+      <c r="E572" t="n">
+        <v>48.67</v>
+      </c>
+      <c r="F572" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="D573" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E573" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="F573" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="D574" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E574" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="F574" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="D575" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="E575" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="F575" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="D576" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="E576" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="F576" t="n">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="D577" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="E577" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="F577" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="D578" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="E578" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="F578" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="D579" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="E579" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="F579" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="D580" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="E580" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="F580" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="D581" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="E581" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="F581" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="D582" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="E582" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="F582" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="D583" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="E583" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="F583" t="n">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="D584" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="E584" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="F584" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="D585" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E585" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="F585" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="D586" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="E586" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="F586" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>58.26</v>
+      </c>
+      <c r="D587" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="E587" t="n">
+        <v>57.92</v>
+      </c>
+      <c r="F587" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="D588" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="E588" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="F588" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="D589" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="E589" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="F589" t="n">
+        <v>58.8</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="D590" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="E590" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="F590" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="D591" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="E591" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F591" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="D592" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="E592" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="F592" t="n">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="D593" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="E593" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="F593" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="D594" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="E594" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="F594" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D595" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="E595" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="F595" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="D596" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="E596" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="F596" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D597" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="E597" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="F597" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="D598" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="E598" t="n">
+        <v>47.39</v>
+      </c>
+      <c r="F598" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="D599" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="E599" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="F599" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="D600" t="n">
+        <v>47.69</v>
+      </c>
+      <c r="E600" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="F600" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="D601" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="E601" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="F601" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="D602" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E602" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="F602" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="D603" t="n">
+        <v>60.01</v>
+      </c>
+      <c r="E603" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="F603" t="n">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="D604" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="E604" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="F604" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="D605" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="E605" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="F605" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="D606" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="E606" t="n">
+        <v>47.38</v>
+      </c>
+      <c r="F606" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="D607" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="E607" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="F607" t="n">
+        <v>59.6</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="D608" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="E608" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F608" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="D609" t="n">
+        <v>60.38</v>
+      </c>
+      <c r="E609" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="F609" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="D610" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="E610" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="F610" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="D611" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="E611" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="F611" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D612" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="E612" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="F612" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="D613" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="E613" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="F613" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="D614" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="E614" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="F614" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="n">
+        <v>46016</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="D615" t="n">
+        <v>60.39</v>
+      </c>
+      <c r="E615" t="n">
+        <v>59.48</v>
+      </c>
+      <c r="F615" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="D616" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="E616" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="F616" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="D617" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="E617" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="F617" t="n">
+        <v>60.1</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="D618" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="E618" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="F618" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="D619" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="E619" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="F619" t="n">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="D620" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="E620" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="F620" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="D621" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="E621" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="F621" t="n">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="D622" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="E622" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F622" t="n">
+        <v>48.5</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="D623" t="n">
+        <v>60.93</v>
+      </c>
+      <c r="E623" t="n">
+        <v>60.61</v>
+      </c>
+      <c r="F623" t="n">
+        <v>60.8</v>
       </c>
     </row>
   </sheetData>

--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F623"/>
+  <dimension ref="A1:F699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14114,16 +14114,16 @@
         </is>
       </c>
       <c r="C622" t="n">
-        <v>48.48</v>
+        <v>50.87</v>
       </c>
       <c r="D622" t="n">
-        <v>48.65</v>
+        <v>51.16</v>
       </c>
       <c r="E622" t="n">
-        <v>48.3</v>
+        <v>50.68</v>
       </c>
       <c r="F622" t="n">
-        <v>48.5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="623">
@@ -14136,16 +14136,1688 @@
         </is>
       </c>
       <c r="C623" t="n">
-        <v>60.73</v>
+        <v>63.45</v>
       </c>
       <c r="D623" t="n">
-        <v>60.93</v>
+        <v>64.14</v>
       </c>
       <c r="E623" t="n">
-        <v>60.61</v>
+        <v>63.33</v>
       </c>
       <c r="F623" t="n">
-        <v>60.8</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="D624" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E624" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="F624" t="n">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>64.86</v>
+      </c>
+      <c r="D625" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="E625" t="n">
+        <v>64.56</v>
+      </c>
+      <c r="F625" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="D626" t="n">
+        <v>51.61</v>
+      </c>
+      <c r="E626" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="F626" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="D627" t="n">
+        <v>65.58</v>
+      </c>
+      <c r="E627" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="F627" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="D628" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="E628" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="F628" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="D629" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="E629" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="F629" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="D630" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="E630" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="F630" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>65.66</v>
+      </c>
+      <c r="D631" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="E631" t="n">
+        <v>65.36</v>
+      </c>
+      <c r="F631" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="D632" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="E632" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="F632" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="D633" t="n">
+        <v>67.31999999999999</v>
+      </c>
+      <c r="E633" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="F633" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="D634" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="E634" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="F634" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="D635" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="E635" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F635" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="D636" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="E636" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="F636" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>67.64</v>
+      </c>
+      <c r="D637" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E637" t="n">
+        <v>67.42</v>
+      </c>
+      <c r="F637" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="D638" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="E638" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="F638" t="n">
+        <v>53.4</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="D639" t="n">
+        <v>69.08</v>
+      </c>
+      <c r="E639" t="n">
+        <v>68.66</v>
+      </c>
+      <c r="F639" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="D640" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="E640" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="F640" t="n">
+        <v>53.6</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="D641" t="n">
+        <v>70</v>
+      </c>
+      <c r="E641" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="F641" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="D642" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="E642" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="F642" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="D643" t="n">
+        <v>71</v>
+      </c>
+      <c r="E643" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="F643" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="D644" t="n">
+        <v>55.03</v>
+      </c>
+      <c r="E644" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="F644" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="D645" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E645" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="F645" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="D646" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="E646" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="F646" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="D647" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="E647" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="F647" t="n">
+        <v>70.90000000000001</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="D648" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="E648" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="F648" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="D649" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="E649" t="n">
+        <v>70.66</v>
+      </c>
+      <c r="F649" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="D650" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="E650" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="F650" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="D651" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="E651" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="F651" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="D652" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="E652" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="F652" t="n">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="D653" t="n">
+        <v>71.48</v>
+      </c>
+      <c r="E653" t="n">
+        <v>70.28</v>
+      </c>
+      <c r="F653" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="D654" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="E654" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="F654" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="D655" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="E655" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="F655" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>54.09</v>
+      </c>
+      <c r="D656" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="E656" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="F656" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>70.17</v>
+      </c>
+      <c r="D657" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="E657" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="F657" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="D658" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E658" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F658" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="D659" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="E659" t="n">
+        <v>70.41</v>
+      </c>
+      <c r="F659" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="D660" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="E660" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="F660" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="D661" t="n">
+        <v>71.45999999999999</v>
+      </c>
+      <c r="E661" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="F661" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="D662" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="E662" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F662" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="D663" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="E663" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="F663" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>54</v>
+      </c>
+      <c r="D664" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="E664" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="F664" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D665" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="E665" t="n">
+        <v>70.06</v>
+      </c>
+      <c r="F665" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="D666" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="E666" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="F666" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>71</v>
+      </c>
+      <c r="D667" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E667" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="F667" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="D668" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="E668" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="F668" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="D669" t="n">
+        <v>70.81</v>
+      </c>
+      <c r="E669" t="n">
+        <v>70.19</v>
+      </c>
+      <c r="F669" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="D670" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="E670" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="F670" t="n">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="D671" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="E671" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="F671" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="D672" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="E672" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="F672" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="D673" t="n">
+        <v>70.88</v>
+      </c>
+      <c r="E673" t="n">
+        <v>70.31999999999999</v>
+      </c>
+      <c r="F673" t="n">
+        <v>70.59999999999999</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="D674" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="E674" t="n">
+        <v>53.53</v>
+      </c>
+      <c r="F674" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="D675" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="E675" t="n">
+        <v>70.66</v>
+      </c>
+      <c r="F675" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="D676" t="n">
+        <v>54.03</v>
+      </c>
+      <c r="E676" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="F676" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>70.06999999999999</v>
+      </c>
+      <c r="D677" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="E677" t="n">
+        <v>69.88</v>
+      </c>
+      <c r="F677" t="n">
+        <v>70.7</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="D678" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="E678" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="F678" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>70.77</v>
+      </c>
+      <c r="D679" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="E679" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="F679" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="D680" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="E680" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="F680" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="D681" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="E681" t="n">
+        <v>70.38</v>
+      </c>
+      <c r="F681" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>54.46</v>
+      </c>
+      <c r="D682" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="E682" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="F682" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="D683" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="E683" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="F683" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="D684" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="E684" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="F684" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>70.13</v>
+      </c>
+      <c r="D685" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="E685" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="F685" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="D686" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="E686" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="F686" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="D687" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="E687" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="F687" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="D688" t="n">
+        <v>55.08</v>
+      </c>
+      <c r="E688" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="F688" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>70.31</v>
+      </c>
+      <c r="D689" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="E689" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="F689" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="D690" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="E690" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="F690" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="D691" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="E691" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="F691" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="D692" t="n">
+        <v>55.44</v>
+      </c>
+      <c r="E692" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="F692" t="n">
+        <v>55.3</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="D693" t="n">
+        <v>71.70999999999999</v>
+      </c>
+      <c r="E693" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="F693" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>55.47</v>
+      </c>
+      <c r="D694" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="E694" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="F694" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="D695" t="n">
+        <v>71.11</v>
+      </c>
+      <c r="E695" t="n">
+        <v>70.67</v>
+      </c>
+      <c r="F695" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="D696" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="E696" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F696" t="n">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="D697" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="E697" t="n">
+        <v>70.59</v>
+      </c>
+      <c r="F697" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="D698" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="E698" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="F698" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>70.26000000000001</v>
+      </c>
+      <c r="D699" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="E699" t="n">
+        <v>70.23999999999999</v>
+      </c>
+      <c r="F699" t="n">
+        <v>70.8</v>
       </c>
     </row>
   </sheetData>

--- a/价格数据初步调整_客户B.xlsx
+++ b/价格数据初步调整_客户B.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F699"/>
+  <dimension ref="A1:F789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15820,6 +15820,1986 @@
         <v>70.8</v>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="D700" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="E700" t="n">
+        <v>56.64</v>
+      </c>
+      <c r="F700" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="D701" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="E701" t="n">
+        <v>70.45999999999999</v>
+      </c>
+      <c r="F701" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>56.82</v>
+      </c>
+      <c r="D702" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="E702" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="F702" t="n">
+        <v>56.9</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="D703" t="n">
+        <v>70.89</v>
+      </c>
+      <c r="E703" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F703" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>57</v>
+      </c>
+      <c r="D704" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="E704" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F704" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="D705" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="E705" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="F705" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D706" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="E706" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="F706" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="D707" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="E707" t="n">
+        <v>71.11</v>
+      </c>
+      <c r="F707" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="D708" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E708" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="F708" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="D709" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="E709" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="F709" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="D710" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="E710" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="F710" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="D711" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="E711" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="F711" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D712" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="E712" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="F712" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="D713" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="E713" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="F713" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="D714" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="E714" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="F714" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D715" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="E715" t="n">
+        <v>71</v>
+      </c>
+      <c r="F715" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D716" t="n">
+        <v>58.31</v>
+      </c>
+      <c r="E716" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="F716" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="D717" t="n">
+        <v>72</v>
+      </c>
+      <c r="E717" t="n">
+        <v>71.69</v>
+      </c>
+      <c r="F717" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="D718" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="E718" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="F718" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="D719" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="E719" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="F719" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="D720" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E720" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="F720" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="D721" t="n">
+        <v>72.59</v>
+      </c>
+      <c r="E721" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="F721" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D722" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="E722" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F722" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="D723" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="E723" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="F723" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="D724" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="E724" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="F724" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="D725" t="n">
+        <v>72.54000000000001</v>
+      </c>
+      <c r="E725" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="F725" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="D726" t="n">
+        <v>57.85</v>
+      </c>
+      <c r="E726" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="F726" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>71.22</v>
+      </c>
+      <c r="D727" t="n">
+        <v>72</v>
+      </c>
+      <c r="E727" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="F727" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="D728" t="n">
+        <v>58.04</v>
+      </c>
+      <c r="E728" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="F728" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="D729" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="E729" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="F729" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="D730" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="E730" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F730" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>72.36</v>
+      </c>
+      <c r="D731" t="n">
+        <v>72.59</v>
+      </c>
+      <c r="E731" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="F731" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="D732" t="n">
+        <v>57.83</v>
+      </c>
+      <c r="E732" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="F732" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D733" t="n">
+        <v>72.01000000000001</v>
+      </c>
+      <c r="E733" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="F733" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="D734" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="E734" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="F734" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="D735" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="E735" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="F735" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="D736" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="E736" t="n">
+        <v>56.89</v>
+      </c>
+      <c r="F736" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="D737" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="E737" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="F737" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="D738" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="E738" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="F738" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="D739" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="E739" t="n">
+        <v>70.81</v>
+      </c>
+      <c r="F739" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>57.29</v>
+      </c>
+      <c r="D740" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="E740" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="F740" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>71.11</v>
+      </c>
+      <c r="D741" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="E741" t="n">
+        <v>70.78</v>
+      </c>
+      <c r="F741" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="D742" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="E742" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="F742" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="D743" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="E743" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="F743" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="D744" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="E744" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F744" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D745" t="n">
+        <v>71.91</v>
+      </c>
+      <c r="E745" t="n">
+        <v>71.09</v>
+      </c>
+      <c r="F745" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>56.69</v>
+      </c>
+      <c r="D746" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="E746" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="F746" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="D747" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="E747" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="F747" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="D748" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="E748" t="n">
+        <v>57.01</v>
+      </c>
+      <c r="F748" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="D749" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="E749" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="F749" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="D750" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E750" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="F750" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="D751" t="n">
+        <v>71.45999999999999</v>
+      </c>
+      <c r="E751" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="F751" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="D752" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="E752" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="F752" t="n">
+        <v>57.3</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="D753" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="E753" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="F753" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="D754" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E754" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="F754" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>71.37</v>
+      </c>
+      <c r="D755" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="E755" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="F755" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="D756" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E756" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F756" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>70.91</v>
+      </c>
+      <c r="D757" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="E757" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="F757" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="D758" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="E758" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="F758" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="D759" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="E759" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="F759" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="D760" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="E760" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="F760" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="D761" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="E761" t="n">
+        <v>71</v>
+      </c>
+      <c r="F761" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="D762" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="E762" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="F762" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="D763" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E763" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="F763" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="D764" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="E764" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="F764" t="n">
+        <v>57.8</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C765" t="n">
+        <v>70.93000000000001</v>
+      </c>
+      <c r="D765" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="E765" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F765" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C766" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="D766" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="E766" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="F766" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="D767" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="E767" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="F767" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="D768" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="E768" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="F768" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="D769" t="n">
+        <v>72.13</v>
+      </c>
+      <c r="E769" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="F769" t="n">
+        <v>71.3</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="D770" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E770" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="F770" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="D771" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="E771" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="F771" t="n">
+        <v>71.40000000000001</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="D772" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="E772" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="F772" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="D773" t="n">
+        <v>71.56</v>
+      </c>
+      <c r="E773" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="F773" t="n">
+        <v>71.40000000000001</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="D774" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="E774" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="F774" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="D775" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E775" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="F775" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="D776" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="E776" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F776" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="D777" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="E777" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="F777" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="D778" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="E778" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="F778" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="D779" t="n">
+        <v>71.98</v>
+      </c>
+      <c r="E779" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="F779" t="n">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="D780" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="E780" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="F780" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="D781" t="n">
+        <v>72</v>
+      </c>
+      <c r="E781" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="F781" t="n">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="D782" t="n">
+        <v>58.58</v>
+      </c>
+      <c r="E782" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="F782" t="n">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>71.73</v>
+      </c>
+      <c r="D783" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="E783" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="F783" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D784" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="E784" t="n">
+        <v>57.87</v>
+      </c>
+      <c r="F784" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="D785" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="E785" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="F785" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>58.12</v>
+      </c>
+      <c r="D786" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="E786" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="F786" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="D787" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="E787" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="F787" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>牛前八件套</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="D788" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="E788" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="F788" t="n">
+        <v>58.1</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>龟排腱</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="D789" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="E789" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="F789" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
